--- a/currentbuild/StructureDefinition-lmdi-medicationadministration.xlsx
+++ b/currentbuild/StructureDefinition-lmdi-medicationadministration.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.4</t>
+    <t>1.1.5</t>
   </si>
   <si>
     <t>Name</t>

--- a/currentbuild/StructureDefinition-lmdi-medicationadministration.xlsx
+++ b/currentbuild/StructureDefinition-lmdi-medicationadministration.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.6</t>
+    <t>1.1.7</t>
   </si>
   <si>
     <t>Name</t>

--- a/currentbuild/StructureDefinition-lmdi-medicationadministration.xlsx
+++ b/currentbuild/StructureDefinition-lmdi-medicationadministration.xlsx
@@ -537,7 +537,7 @@
     <t>Angir om legemiddeladministreringen er utført eller om en tidligere registrert administrering er feilregistrert. completed brukes for en utført administrering. entered-in-error brukes når en tidligere rapportert administrering skal annulleres/slettes fordi registreringen ikke representerer en gyldig administrering.</t>
   </si>
   <si>
-    <t>Ved korrigering/endring av opplysninger om en tidligere rapportert administrering skal ressursen rapporteres på nytt med samme identifikator og korrigerte opplysninger. Ved annullering/sletting skal den rapporteres på nytt med samme identifikator og status entered-in-error. En tidligere rapportert administrering skal ikke annulleres/slettes ved bare å utelate den fra senere innsendinger.</t>
+    <t>Ved korrigering/endring av opplysninger om en tidligere rapportert administrering skal ressursen rapporteres på nytt med samme identifikator (identifier) og korrigerte opplysninger. Ved annullering/sletting skal den rapporteres på nytt med samme identifikator (identifier) og status entered-in-error. En tidligere rapportert administrering skal ikke annulleres/slettes ved bare å utelate den fra senere innsendinger.</t>
   </si>
   <si>
     <t>required</t>

--- a/currentbuild/StructureDefinition-lmdi-medicationadministration.xlsx
+++ b/currentbuild/StructureDefinition-lmdi-medicationadministration.xlsx
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Beskriver administrering av legemiddel til pasient på institusjon. Dette er kjerneressursen for denne implementasjonsguiden. Den peker videre til legemiddelet som ble gitt, pasienten som har fått administrert legemiddel, episoden administreringen skjedde i løpet av (som igjen peker på hvilken institusjon det skjedde ved), organisasjonen administreringen ble utført ved (administrertVed, når episoden gjelder hele innleggelsen), rekvireringen administreringen var basert på og årsaken (diagnosen) til at legemidlet ble gitt.
+    <t>Beskriver administrering av legemiddel til pasient på institusjon. Dette er kjerneressursen for denne implementasjonsguiden. Den peker videre til legemiddelet som ble gitt, pasienten som har fått administrert legemiddel, episoden administreringen skjedde i løpet av (som igjen peker på hvilken institusjon episoden skjedde ved), organisasjonen administreringen ble utført ved (administrertVed, når episoden gjelder hele innleggelsen), rekvireringen administreringen var basert på og årsaken (diagnosen) til at legemidlet ble gitt.
 Dersom opplysninger om en tidligere rapportert administrering korrigeres/endres eller administreringen annulleres/slettes, skal administreringen rapporteres på nytt med samme identifikator (identifier). Ved annullering/sletting brukes status entered-in-error.</t>
   </si>
   <si>
